--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="435">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-lab</t>
+    <t>http://va.gov/fhir/StructureDefinition/LabObservationDiagnosticReport</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -818,6 +818,74 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-2:1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB {null}</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>DiagnosticReport.category:LaboratorySlice</t>
@@ -868,67 +936,6 @@
     <t>FiveWs.what[x]</t>
   </si>
   <si>
-    <t>DiagnosticReport.code.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1536: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - LAB SECTION &gt; LAB SECTION - NAME (#63.05-.35 &gt; 63.5-9 &gt; 62-6 &gt; 62.2-.01)</t>
-  </si>
-  <si>
     <t>DiagnosticReport.subject</t>
   </si>
   <si>
@@ -959,6 +966,30 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Pathology.Autopsy.LRDFN
+Micro.BacteriologyReports.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+SStaff.SMicroOrderedTest.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -1745,7 +1776,7 @@
     <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="189.48828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="165.01953125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="57.953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4404,42 +4435,38 @@
         <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4449,7 +4476,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4464,13 +4491,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4488,31 +4515,31 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4523,42 +4550,42 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>166</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4584,55 +4611,55 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4643,10 +4670,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4657,7 +4684,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4666,19 +4693,23 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4726,34 +4757,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>164</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4761,21 +4792,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4784,21 +4815,23 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>273</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4834,46 +4867,46 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>164</v>
+        <v>278</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4881,24 +4914,26 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -4907,20 +4942,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4929,7 +4962,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -4944,13 +4977,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4968,7 +5001,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4986,13 +5019,13 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5010,17 +5043,17 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5029,20 +5062,18 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O28" t="s" s="2">
         <v>287</v>
       </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5066,13 +5097,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5090,10 +5121,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
@@ -5105,19 +5136,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5125,14 +5156,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5151,17 +5182,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5210,7 +5241,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5225,34 +5256,34 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5271,19 +5302,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5332,7 +5363,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5347,16 +5378,16 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5367,14 +5398,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5393,19 +5424,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5442,7 +5473,7 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -5452,7 +5483,7 @@
         <v>169</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5461,22 +5492,22 @@
         <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5487,16 +5518,16 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5515,19 +5546,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5576,7 +5607,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5585,40 +5616,40 @@
         <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5637,19 +5668,19 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5698,7 +5729,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5707,7 +5738,7 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
@@ -5716,31 +5747,31 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5759,19 +5790,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5820,7 +5851,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5835,19 +5866,19 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -5855,14 +5886,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5881,19 +5912,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5942,7 +5973,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5957,16 +5988,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5977,10 +6008,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6003,19 +6034,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6064,7 +6095,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6082,10 +6113,10 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6099,14 +6130,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6125,19 +6156,19 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6186,7 +6217,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6204,16 +6235,16 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6221,10 +6252,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6247,16 +6278,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6306,7 +6337,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6327,7 +6358,7 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6341,14 +6372,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6367,17 +6398,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6426,7 +6457,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6444,10 +6475,10 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6461,10 +6492,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6579,10 +6610,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6699,14 +6730,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6728,10 +6759,10 @@
         <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>140</v>
@@ -6786,7 +6817,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6821,10 +6852,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6850,16 +6881,16 @@
         <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6908,7 +6939,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6929,7 +6960,7 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6943,10 +6974,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6969,13 +7000,13 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7026,7 +7057,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>91</v>
@@ -7047,7 +7078,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7061,14 +7092,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7090,14 +7121,14 @@
         <v>160</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7146,7 +7177,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7164,10 +7195,10 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7181,10 +7212,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7210,10 +7241,10 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7243,28 +7274,28 @@
         <v>251</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="Z46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7282,10 +7313,10 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7299,10 +7330,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7325,19 +7356,19 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7386,7 +7417,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7404,10 +7435,10 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1256,7 +1256,7 @@
     <t>outboundRelationship[typeCode=COMP].target</t>
   </si>
   <si>
-    <t>++: reference from null (#null)</t>
+    <t>++: reference</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA MICROBIOLOGY (file 63.05) to FHIR DiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to LabObservationDiagnosticReport</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$43</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology {DiagnosticReport}</t>
+    <t>Lab Observation: Microbiology DiagnosticReport</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to LabObservationDiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/LabObservationDiagnosticReport</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -818,74 +818,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-2:1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB {null}</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>DiagnosticReport.category:LaboratorySlice</t>
@@ -966,30 +898,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -1734,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP47"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -1776,7 +1684,7 @@
     <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="143.84765625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="57.953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3733,7 +3641,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
@@ -4435,38 +4343,42 @@
         <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4476,7 +4388,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4491,13 +4403,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4515,31 +4427,31 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4550,42 +4462,42 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4611,55 +4523,55 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4670,24 +4582,24 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4696,19 +4608,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4757,34 +4667,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>267</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4792,14 +4702,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4818,19 +4728,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4879,7 +4789,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4894,19 +4804,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4914,20 +4824,18 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -4942,18 +4850,20 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4962,7 +4872,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -4977,55 +4887,53 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5036,18 +4944,20 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5062,18 +4972,20 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>308</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5097,13 +5009,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5121,53 +5033,53 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5182,17 +5094,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5241,7 +5155,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5250,50 +5164,50 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5302,19 +5216,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5363,13 +5277,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5378,19 +5292,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5398,24 +5312,24 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5424,19 +5338,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5473,41 +5387,43 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5518,47 +5434,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5607,56 +5521,56 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>92</v>
@@ -5665,22 +5579,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5729,16 +5643,16 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
@@ -5747,31 +5661,31 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5781,29 +5695,27 @@
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5851,7 +5763,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5866,19 +5778,19 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -5886,14 +5798,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5912,19 +5824,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5973,7 +5883,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5988,16 +5898,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6008,10 +5918,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6022,7 +5932,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6034,20 +5944,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>368</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6095,28 +6001,28 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6137,7 +6043,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>375</v>
+        <v>136</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6147,7 +6053,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6156,20 +6062,18 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>138</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6217,7 +6121,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6229,22 +6133,22 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>164</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6252,14 +6156,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6272,24 +6176,26 @@
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>385</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6337,7 +6243,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6349,7 +6255,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6358,7 +6264,7 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>389</v>
+        <v>134</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6372,21 +6278,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6395,20 +6301,22 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>392</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6457,13 +6365,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6475,10 +6383,10 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6492,10 +6400,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6503,7 +6411,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -6515,16 +6423,16 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>387</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>388</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
+        <v>389</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6575,10 +6483,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -6587,7 +6495,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6596,7 +6504,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>164</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6610,21 +6518,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>392</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6636,18 +6544,18 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>393</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6695,28 +6603,28 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>391</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>164</v>
+        <v>397</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6730,14 +6638,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6750,26 +6658,22 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6793,13 +6697,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6817,7 +6721,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6829,16 +6733,16 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>134</v>
+        <v>403</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6866,7 +6770,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6878,19 +6782,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>405</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6945,7 +6849,7 @@
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6957,10 +6861,10 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6969,489 +6873,11 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP47">
+  <autoFilter ref="A1:AP43">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7461,7 +6887,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI42">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -746,6 +746,9 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.05-.35 &gt; 63.5-3)</t>
   </si>
   <si>
     <t>DiagnosticReport.status</t>
@@ -1059,7 +1062,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole)
 </t>
   </si>
   <si>
@@ -1087,7 +1090,7 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>1434: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+    <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (#63.05-.112)</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -1142,7 +1145,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyObservation)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab)
 </t>
   </si>
   <si>
@@ -1162,9 +1165,6 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>++: reference</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>
@@ -1655,7 +1655,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.3515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3999,7 +3999,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
@@ -4096,7 +4096,7 @@
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4133,14 +4133,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4187,7 +4187,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4196,25 +4196,25 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4222,14 +4222,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4251,13 +4251,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4283,19 +4283,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4305,7 +4305,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4323,13 +4323,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4340,16 +4340,16 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4371,13 +4371,13 @@
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4388,7 +4388,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4403,13 +4403,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4427,7 +4427,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4445,13 +4445,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4462,14 +4462,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4491,13 +4491,13 @@
         <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4526,10 +4526,10 @@
         <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4547,7 +4547,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -4562,16 +4562,16 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4582,14 +4582,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4608,17 +4608,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4667,7 +4667,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4682,16 +4682,16 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -4702,14 +4702,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4728,19 +4728,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4789,7 +4789,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4804,16 +4804,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4824,14 +4824,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4850,19 +4850,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4899,7 +4899,7 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -4909,7 +4909,7 @@
         <v>169</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4918,22 +4918,22 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -4944,16 +4944,16 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4972,19 +4972,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5033,7 +5033,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5042,40 +5042,40 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5094,19 +5094,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5155,7 +5155,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5164,7 +5164,7 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
@@ -5173,31 +5173,31 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5216,19 +5216,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5277,7 +5277,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5292,19 +5292,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5312,14 +5312,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5338,19 +5338,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5399,7 +5399,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5414,16 +5414,16 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5460,19 +5460,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5521,7 +5521,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5539,10 +5539,10 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5556,14 +5556,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5582,19 +5582,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5643,7 +5643,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5661,16 +5661,16 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5904,7 +5904,7 @@
         <v>372</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6697,7 +6697,7 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Y42" t="s" s="2">
         <v>401</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,7 +729,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -1111,7 +1111,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1319,7 +1319,7 @@
     <t>va-by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1335,7 +1335,7 @@
     <t>va-at</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -772,7 +772,7 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
+    <t>http://va.gov/fhir/ValueSet/DiagnosticReportLabStatus</t>
   </si>
   <si>
     <t>us-core-8

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1133,7 +1133,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1944,7 +1944,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1133,8 +1133,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1276,6 +1275,9 @@
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
+    <t>Documents.ToTime,LabOrder.Result.ResultTime</t>
+  </si>
+  <si>
     <t>OBR-22</t>
   </si>
   <si>
@@ -1336,6 +1338,9 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
+    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+  </si>
+  <si>
     <t>DiagnosticReport.performer:va-at</t>
   </si>
   <si>
@@ -1350,6 +1355,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
+  </si>
+  <si>
+    <t>Documents.EnteredAt,LabOrder.Result.EnteredAt</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -1944,7 +1952,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>
@@ -7374,31 +7382,31 @@
         <v>402</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7417,19 +7425,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7476,7 +7484,7 @@
         <v>170</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7500,30 +7508,30 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7542,19 +7550,19 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7603,7 +7611,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7618,39 +7626,39 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7669,19 +7677,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7730,7 +7738,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7745,37 +7753,37 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7794,19 +7802,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7855,7 +7863,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7879,24 +7887,24 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7919,19 +7927,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7980,7 +7988,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8007,7 +8015,7 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>362</v>
@@ -8018,14 +8026,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8044,19 +8052,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8105,7 +8113,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8120,7 +8128,7 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8132,10 +8140,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8143,10 +8151,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8169,16 +8177,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8228,7 +8236,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8258,7 +8266,7 @@
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8266,14 +8274,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8292,17 +8300,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8351,7 +8359,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8378,10 +8386,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8389,10 +8397,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8510,10 +8518,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8633,14 +8641,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8662,10 +8670,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -8720,7 +8728,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8758,10 +8766,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8787,16 +8795,16 @@
         <v>161</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8845,7 +8853,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8875,7 +8883,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8883,10 +8891,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8909,13 +8917,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8966,7 +8974,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8996,7 +9004,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9004,14 +9012,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9033,14 +9041,14 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9089,7 +9097,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9116,10 +9124,10 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9127,10 +9135,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9156,10 +9164,10 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9189,28 +9197,28 @@
         <v>257</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9237,10 +9245,10 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9248,10 +9256,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9274,19 +9282,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9335,7 +9343,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9362,10 +9370,10 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1133,7 +1133,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1338,7 +1338,7 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
-    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+    <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>DiagnosticReport.performer:va-at</t>
@@ -1952,7 +1952,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-diagnosticreport-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1308,6 +1308,10 @@
   </si>
   <si>
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -7474,7 +7478,7 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>260</v>
+        <v>414</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -7508,27 +7512,27 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>407</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>408</v>
@@ -7550,7 +7554,7 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>410</v>
@@ -7626,36 +7630,36 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>407</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>408</v>
@@ -7677,7 +7681,7 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>410</v>
@@ -7753,37 +7757,37 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7802,16 +7806,16 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>413</v>
@@ -7863,7 +7867,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7887,24 +7891,24 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7927,19 +7931,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7988,7 +7992,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8015,7 +8019,7 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>362</v>
@@ -8026,14 +8030,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8052,19 +8056,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8113,7 +8117,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8128,7 +8132,7 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8140,10 +8144,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8151,10 +8155,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8177,16 +8181,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8236,7 +8240,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8266,7 +8270,7 @@
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8274,14 +8278,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8300,17 +8304,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8359,7 +8363,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8386,10 +8390,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8397,10 +8401,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8518,10 +8522,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8641,14 +8645,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8670,10 +8674,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -8728,7 +8732,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8766,10 +8770,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8795,16 +8799,16 @@
         <v>161</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8853,7 +8857,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8883,7 +8887,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8891,10 +8895,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8917,13 +8921,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8974,7 +8978,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -9004,7 +9008,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9012,14 +9016,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9041,14 +9045,14 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9097,7 +9101,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9124,10 +9128,10 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9135,10 +9139,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9164,10 +9168,10 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9197,10 +9201,10 @@
         <v>257</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9218,7 +9222,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9245,10 +9249,10 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9256,10 +9260,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9282,19 +9286,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9343,7 +9347,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9370,10 +9374,10 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -669,7 +669,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1605: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (63.05-.35 &gt; 63.5-.001)</t>
+    <t>1605: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (63.05-.35 &gt; 63.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -748,7 +748,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.05-.35 &gt; 63.5-3)</t>
+    <t>1690: reference based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.05-.35 &gt; 63.5-3)</t>
   </si>
   <si>
     <t>Micro.MicroOrderedTest.CPRSOrderIEN,SStaff.SMicroOrderedTest.CPRSOrderIEN</t>
@@ -890,7 +890,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
@@ -962,7 +962,7 @@
     <t>DiagnosticReport.code.coding</t>
   </si>
   <si>
-    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+    <t>1420: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding.id</t>
@@ -1037,7 +1037,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
+    <t>1420-1: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1061,7 +1061,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
+    <t>1420-3: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1101,7 +1101,7 @@
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
-    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+    <t>1661: source value based on LABORATORY TEST - NAME (60-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.LabChemTestName</t>
@@ -1127,7 +1127,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1236,7 +1236,7 @@
 </t>
   </si>
   <si>
-    <t>1424: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
+    <t>1424: source value based on MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
@@ -1269,7 +1269,7 @@
 </t>
   </si>
   <si>
-    <t>1429: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
+    <t>1429: source value based on MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1336,7 +1336,7 @@
 </t>
   </si>
   <si>
-    <t>1434: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+    <t>1434: reference based on MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
@@ -1355,7 +1355,7 @@
 </t>
   </si>
   <si>
-    <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+    <t>1682: reference based on MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
@@ -1432,7 +1432,7 @@
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
   </si>
   <si>
-    <t>1437: reference from See mapping for Lab Observation</t>
+    <t>1437: reference based on See mapping for Lab Observation</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -1954,7 +1954,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="167.57421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
   </si>
   <si>
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_DiagnosticReportLabStatus](ConceptMap-VF-DiagnosticReportLabStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/DiagnosticReportLabStatus</t>
@@ -4502,9 +4505,11 @@
       <c r="X21" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y21" s="2"/>
+      <c r="Y21" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -4531,43 +4536,43 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4589,13 +4594,13 @@
         <v>183</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4621,19 +4626,19 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4643,7 +4648,7 @@
         <v>170</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4670,21 +4675,21 @@
         <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4802,10 +4807,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4925,10 +4930,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4951,19 +4956,19 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5012,7 +5017,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5039,10 +5044,10 @@
         <v>83</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>83</v>
@@ -5050,10 +5055,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5079,16 +5084,16 @@
         <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5137,7 +5142,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5152,10 +5157,10 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
@@ -5164,10 +5169,10 @@
         <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5175,16 +5180,16 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5206,13 +5211,13 @@
         <v>183</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5223,7 +5228,7 @@
         <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>83</v>
@@ -5238,13 +5243,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5262,7 +5267,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5277,7 +5282,7 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
@@ -5289,25 +5294,25 @@
         <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5329,13 +5334,13 @@
         <v>183</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5364,10 +5369,10 @@
         <v>188</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5385,7 +5390,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5409,24 +5414,24 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5544,10 +5549,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5667,10 +5672,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5693,19 +5698,19 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5754,7 +5759,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5769,10 +5774,10 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>83</v>
@@ -5781,10 +5786,10 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5792,10 +5797,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5913,10 +5918,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6036,10 +6041,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6065,16 +6070,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6084,7 +6089,7 @@
         <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>83</v>
@@ -6123,7 +6128,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6138,7 +6143,7 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
@@ -6150,10 +6155,10 @@
         <v>83</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6161,10 +6166,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6190,13 +6195,13 @@
         <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6246,7 +6251,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6273,10 +6278,10 @@
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -6284,10 +6289,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6313,14 +6318,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6369,7 +6374,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6384,10 +6389,10 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>83</v>
@@ -6396,10 +6401,10 @@
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6407,10 +6412,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6436,14 +6441,14 @@
         <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6492,7 +6497,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6507,10 +6512,10 @@
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>83</v>
@@ -6519,10 +6524,10 @@
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6530,10 +6535,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6556,19 +6561,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6617,7 +6622,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6644,10 +6649,10 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
@@ -6655,10 +6660,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6684,16 +6689,16 @@
         <v>161</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6742,7 +6747,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6757,10 +6762,10 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>83</v>
@@ -6769,10 +6774,10 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6780,14 +6785,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6806,17 +6811,17 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6865,7 +6870,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6880,37 +6885,37 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6929,19 +6934,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6990,7 +6995,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7014,28 +7019,28 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7054,19 +7059,19 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7103,7 +7108,7 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7113,7 +7118,7 @@
         <v>170</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7122,7 +7127,7 @@
         <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>104</v>
@@ -7137,30 +7142,30 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7179,19 +7184,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7240,7 +7245,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7249,43 +7254,43 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7304,19 +7309,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7365,7 +7370,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7374,43 +7379,43 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7429,19 +7434,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7478,7 +7483,7 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -7488,7 +7493,7 @@
         <v>170</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7512,30 +7517,30 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7554,19 +7559,19 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7615,7 +7620,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7630,39 +7635,39 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7681,19 +7686,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7742,7 +7747,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7757,37 +7762,37 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7806,19 +7811,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7867,7 +7872,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7891,24 +7896,24 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7931,19 +7936,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7992,7 +7997,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8019,10 +8024,10 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8030,14 +8035,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8056,19 +8061,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8117,7 +8122,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8132,7 +8137,7 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8144,10 +8149,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8155,10 +8160,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8181,16 +8186,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8240,7 +8245,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8270,7 +8275,7 @@
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8278,14 +8283,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8304,17 +8309,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8363,7 +8368,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8390,10 +8395,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8401,10 +8406,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8522,10 +8527,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8645,14 +8650,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8674,10 +8679,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -8732,7 +8737,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8770,10 +8775,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8799,16 +8804,16 @@
         <v>161</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8857,7 +8862,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8887,7 +8892,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8895,10 +8900,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8921,13 +8926,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8978,7 +8983,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -9008,7 +9013,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9016,14 +9021,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9045,14 +9050,14 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9101,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9128,10 +9133,10 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9139,10 +9144,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9168,10 +9173,10 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9198,13 +9203,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9222,7 +9227,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9249,10 +9254,10 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9260,10 +9265,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9286,19 +9291,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9347,7 +9352,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9374,10 +9379,10 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1419,7 +1419,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationObservation)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyObservation)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1130,13 +1130,11 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
-  </si>
-  <si>
-    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lomdr-42-1421:If PATIENT - LABORATORY REFERENCE (2-63) == LAB DATA – LRDFN (63-.01) then reference /Patient based on (2-) {true}</t>
+  </si>
+  <si>
+    <t>1421: reference based on PATIENT - (2-) if PATIENT - LABORATORY REFERENCE (2-63) == LAB DATA – LRDFN (63-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -6882,40 +6880,40 @@
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>358</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>364</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6934,19 +6932,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6995,7 +6993,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7019,28 +7017,28 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>375</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7059,19 +7057,19 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7108,7 +7106,7 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7118,7 +7116,7 @@
         <v>170</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7127,7 +7125,7 @@
         <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>104</v>
@@ -7142,30 +7140,30 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="B43" t="s" s="2">
+      <c r="D43" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="D43" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7184,19 +7182,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7245,7 +7243,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7254,43 +7252,43 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AM43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7309,19 +7307,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7370,7 +7368,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7379,43 +7377,43 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7434,19 +7432,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7483,7 +7481,7 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -7493,7 +7491,7 @@
         <v>170</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7517,30 +7515,30 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AP45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="B46" t="s" s="2">
+      <c r="D46" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7559,19 +7557,19 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7620,7 +7618,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7635,39 +7633,39 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AN46" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="B47" t="s" s="2">
+      <c r="D47" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7686,19 +7684,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7747,7 +7745,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7762,37 +7760,37 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AN47" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7811,19 +7809,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7872,7 +7870,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7896,24 +7894,24 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AP48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7936,19 +7934,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7997,7 +7995,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8024,10 +8022,10 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8035,14 +8033,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8061,19 +8059,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8122,7 +8120,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8137,22 +8135,22 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8160,10 +8158,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8186,16 +8184,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8245,7 +8243,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8275,7 +8273,7 @@
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8283,14 +8281,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8309,17 +8307,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8368,7 +8366,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8395,10 +8393,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8406,10 +8404,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8527,10 +8525,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8650,14 +8648,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8679,10 +8677,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -8737,7 +8735,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8775,10 +8773,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8804,16 +8802,16 @@
         <v>161</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8862,7 +8860,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8892,7 +8890,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8900,10 +8898,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8926,13 +8924,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8983,7 +8981,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -9013,7 +9011,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9021,14 +9019,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9050,14 +9048,14 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9106,7 +9104,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9133,10 +9131,10 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9144,10 +9142,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9173,10 +9171,10 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9206,11 +9204,11 @@
         <v>258</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9227,7 +9225,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9254,10 +9252,10 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9265,10 +9263,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9291,19 +9289,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9352,7 +9350,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9379,10 +9377,10 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
